--- a/docs/PerfionAuningFieldOverview.xlsx
+++ b/docs/PerfionAuningFieldOverview.xlsx
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>`priceWebDeEurStk_DE`</t>
+          <t>`price_DE`</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>`recommendedPriceWebDeEurStk_DE`</t>
+          <t>`recommendedPrice_DE`</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>`campaignPriceWebDeEurStk_DE`</t>
+          <t>`campaignPrice_DE`</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>`priceWebDkLcyStk_DK`</t>
+          <t>`price_DK`</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>`recommendedPriceWebDkLcyStk_DK`</t>
+          <t>`recommendedPrice_DK`</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>`campaignPriceWebDkLcyStk_DK`</t>
+          <t>`campaignPrice_DK`</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>`priceWebNlEurStk_NL`</t>
+          <t>`price_NL`</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>`recommendedPriceWebNlEurStk_NL`</t>
+          <t>`recommendedPrice_NL`</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>`campaignPriceWebNlEurStk_NL`</t>
+          <t>`campaignPrice_NL`</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>`priceWebNoLcyStk_NO`</t>
+          <t>`price_NO`</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>`recommendedPriceWebNoLcyStk_NO`</t>
+          <t>`recommendedPrice_NO`</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>`campaignPriceWebNoLcyStk_NO`</t>
+          <t>`campaignPrice_NO`</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">

--- a/docs/PerfionAuningFieldOverview.xlsx
+++ b/docs/PerfionAuningFieldOverview.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AuningStockDW" sheetId="1" r:id="Rfdaf98e3aec942f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PerfionItemsDW" sheetId="2" r:id="Rcf1ec9f281534cbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PerfionPricesDW" sheetId="3" r:id="Rdc8a50be971449a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AuningStockDW" sheetId="1" r:id="R080e7a32f57a4652"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PerfionItemsDW" sheetId="2" r:id="R8704c78045de47e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PerfionPricesDW" sheetId="3" r:id="R3d79f74938e0445d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -446,7 +446,7 @@
         </x:is>
       </x:c>
       <x:c r="D9" s="6" t="str">
-        <x:v>Snapshotfelt opdateret af `codeunit 50042`. Beregnes som fysisk AUNING-beholdning for blank variant minus salgsordre-demand for blank variant med `Shipment Date &lt;= Today + 30D`, hvor salgsordren er `Open` eller `Released`. Kan reduceres med Job Queue-parameteren `AvailableReductionPct`, rundes ned til heltal og clamps til `0`.</x:v>
+        <x:v>Snapshotfelt opdateret af `codeunit 50042`. Beregnes som Business Central varedisponering for lokation `AUNING`, blank variant og `Date Filter = ..Today+30D`: disponibel beholdning plus planlagte modtagelser minus bruttobehov. Kan reduceres med Job Queue-parameteren `AvailableReductionPct`, rundes ned til heltal og clamps til `0`.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
